--- a/inst/extdata/confederated_salish_and_kootenai_tribe_criteria_crosswalk.xlsx
+++ b/inst/extdata/confederated_salish_and_kootenai_tribe_criteria_crosswalk.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tetratechinc-my.sharepoint.com/personal/hannah_ferriby_tetratech_com/Documents/Documents/GitHub/TADACommunityHub/inst/extdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{BA7B3C12-6042-49B2-BC5D-4E8081FEDC74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6CC5AD23-02F9-4154-86E2-1967F73ADDDA}"/>
+  <xr:revisionPtr revIDLastSave="34" documentId="13_ncr:1_{BA7B3C12-6042-49B2-BC5D-4E8081FEDC74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8E72CB40-0AAE-4F61-8E8F-9C0B296A512F}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{368E602C-310B-402B-BB64-86A968C8A420}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{368E602C-310B-402B-BB64-86A968C8A420}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1872" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1876" uniqueCount="178">
   <si>
     <t>TADA.ComparableDataIdentifier</t>
   </si>
@@ -527,9 +527,6 @@
     <t>pHDirection</t>
   </si>
   <si>
-    <t>TemperatureExtreme</t>
-  </si>
-  <si>
     <t>pH_param_9</t>
   </si>
   <si>
@@ -551,13 +548,28 @@
     <t>MaxEqMagnitude</t>
   </si>
   <si>
-    <t>Min</t>
-  </si>
-  <si>
-    <t>Max</t>
-  </si>
-  <si>
     <t>Equation</t>
+  </si>
+  <si>
+    <t>AmmoniaEqType</t>
+  </si>
+  <si>
+    <t>pH_param_10</t>
+  </si>
+  <si>
+    <t>pH_param_11</t>
+  </si>
+  <si>
+    <t>pH_param_12</t>
+  </si>
+  <si>
+    <t>Overall Min</t>
+  </si>
+  <si>
+    <t>Min Multiplier</t>
+  </si>
+  <si>
+    <t>Max Exponent</t>
   </si>
 </sst>
 </file>
@@ -977,22 +989,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AF54233-7D1D-4ABA-97DA-1E98F45EFE00}">
-  <dimension ref="A1:AX160"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:BA160"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="11" width="9.140625" style="7"/>
-    <col min="12" max="12" width="9.7109375" style="7" customWidth="1"/>
-    <col min="13" max="30" width="9.140625" style="7"/>
-    <col min="31" max="31" width="20.28515625" style="7" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="153" style="7" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="13.5703125" style="7" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="12.7109375" style="7" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="19.7109375" style="7" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="8.85546875" style="7" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="7"/>
+    <col min="1" max="11" width="9.109375" style="7"/>
+    <col min="12" max="12" width="9.6640625" style="7" customWidth="1"/>
+    <col min="13" max="30" width="9.109375" style="7"/>
+    <col min="31" max="31" width="20.33203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="160.5546875" style="7" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="13.5546875" style="7" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="12.88671875" style="7" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="20" style="7" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="10.88671875" style="7" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="17.88671875" style="7" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.109375" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:50" s="5" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:53" s="5" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1087,7 +1100,7 @@
         <v>30</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="AG1" s="1" t="s">
         <v>161</v>
@@ -1108,7 +1121,7 @@
         <v>34</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="AN1" s="1" t="s">
         <v>35</v>
@@ -1123,28 +1136,37 @@
         <v>38</v>
       </c>
       <c r="AR1" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="AS1" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="AT1" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="AU1" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="AV1" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="AW1" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="AX1" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="AY1" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="AZ1" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="AS1" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="AT1" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="AU1" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="AV1" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="AW1" s="8" t="s">
+      <c r="BA1" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="AX1" s="8" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="2" spans="1:50" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:53" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
       <c r="B2" s="3" t="s">
         <v>39</v>
@@ -1218,7 +1240,7 @@
       <c r="AQ2" s="6"/>
       <c r="AR2" s="6"/>
     </row>
-    <row r="3" spans="1:50" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:53" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="3"/>
       <c r="B3" s="3" t="s">
         <v>39</v>
@@ -1292,7 +1314,7 @@
       <c r="AQ3" s="6"/>
       <c r="AR3" s="6"/>
     </row>
-    <row r="4" spans="1:50" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:53" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
       <c r="B4" s="3" t="s">
         <v>39</v>
@@ -1366,7 +1388,7 @@
       <c r="AQ4" s="6"/>
       <c r="AR4" s="6"/>
     </row>
-    <row r="5" spans="1:50" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:53" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="3"/>
       <c r="B5" s="3" t="s">
         <v>39</v>
@@ -1440,7 +1462,7 @@
       <c r="AQ5" s="6"/>
       <c r="AR5" s="6"/>
     </row>
-    <row r="6" spans="1:50" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:53" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="3"/>
       <c r="B6" s="3" t="s">
         <v>39</v>
@@ -1514,7 +1536,7 @@
       <c r="AQ6" s="6"/>
       <c r="AR6" s="6"/>
     </row>
-    <row r="7" spans="1:50" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:53" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="3"/>
       <c r="B7" s="3" t="s">
         <v>39</v>
@@ -1588,7 +1610,7 @@
       <c r="AQ7" s="6"/>
       <c r="AR7" s="6"/>
     </row>
-    <row r="8" spans="1:50" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:53" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="3"/>
       <c r="B8" s="3" t="s">
         <v>39</v>
@@ -1662,7 +1684,7 @@
       <c r="AQ8" s="6"/>
       <c r="AR8" s="6"/>
     </row>
-    <row r="9" spans="1:50" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:53" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="3"/>
       <c r="B9" s="3" t="s">
         <v>39</v>
@@ -1736,7 +1758,7 @@
       <c r="AQ9" s="6"/>
       <c r="AR9" s="6"/>
     </row>
-    <row r="10" spans="1:50" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:53" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="3"/>
       <c r="B10" s="3" t="s">
         <v>39</v>
@@ -1810,7 +1832,7 @@
       <c r="AQ10" s="6"/>
       <c r="AR10" s="6"/>
     </row>
-    <row r="11" spans="1:50" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:53" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="3"/>
       <c r="B11" s="3" t="s">
         <v>39</v>
@@ -1884,7 +1906,7 @@
       <c r="AQ11" s="6"/>
       <c r="AR11" s="6"/>
     </row>
-    <row r="12" spans="1:50" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:53" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="3"/>
       <c r="B12" s="3" t="s">
         <v>39</v>
@@ -1958,7 +1980,7 @@
       <c r="AQ12" s="6"/>
       <c r="AR12" s="6"/>
     </row>
-    <row r="13" spans="1:50" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:53" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="3"/>
       <c r="B13" s="3" t="s">
         <v>39</v>
@@ -2032,7 +2054,7 @@
       <c r="AQ13" s="6"/>
       <c r="AR13" s="6"/>
     </row>
-    <row r="14" spans="1:50" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:53" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="3"/>
       <c r="B14" s="3" t="s">
         <v>39</v>
@@ -2106,7 +2128,7 @@
       <c r="AQ14" s="6"/>
       <c r="AR14" s="6"/>
     </row>
-    <row r="15" spans="1:50" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:53" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="3"/>
       <c r="B15" s="3" t="s">
         <v>39</v>
@@ -2180,7 +2202,7 @@
       <c r="AQ15" s="6"/>
       <c r="AR15" s="6"/>
     </row>
-    <row r="16" spans="1:50" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:53" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="3"/>
       <c r="B16" s="3" t="s">
         <v>39</v>
@@ -2254,7 +2276,7 @@
       <c r="AQ16" s="6"/>
       <c r="AR16" s="6"/>
     </row>
-    <row r="17" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="3"/>
       <c r="B17" s="3" t="s">
         <v>39</v>
@@ -2328,7 +2350,7 @@
       <c r="AQ17" s="6"/>
       <c r="AR17" s="6"/>
     </row>
-    <row r="18" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="3"/>
       <c r="B18" s="3" t="s">
         <v>39</v>
@@ -2402,7 +2424,7 @@
       <c r="AQ18" s="6"/>
       <c r="AR18" s="6"/>
     </row>
-    <row r="19" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="3"/>
       <c r="B19" s="3" t="s">
         <v>39</v>
@@ -2476,7 +2498,7 @@
       <c r="AQ19" s="6"/>
       <c r="AR19" s="6"/>
     </row>
-    <row r="20" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="3"/>
       <c r="B20" s="3" t="s">
         <v>39</v>
@@ -2550,7 +2572,7 @@
       <c r="AQ20" s="6"/>
       <c r="AR20" s="6"/>
     </row>
-    <row r="21" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="3"/>
       <c r="B21" s="3" t="s">
         <v>39</v>
@@ -2624,7 +2646,7 @@
       <c r="AQ21" s="6"/>
       <c r="AR21" s="6"/>
     </row>
-    <row r="22" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="3"/>
       <c r="B22" s="3" t="s">
         <v>39</v>
@@ -2698,7 +2720,7 @@
       <c r="AQ22" s="6"/>
       <c r="AR22" s="6"/>
     </row>
-    <row r="23" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="3"/>
       <c r="B23" s="3" t="s">
         <v>39</v>
@@ -2772,7 +2794,7 @@
       <c r="AQ23" s="6"/>
       <c r="AR23" s="6"/>
     </row>
-    <row r="24" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="3"/>
       <c r="B24" s="3" t="s">
         <v>39</v>
@@ -2846,7 +2868,7 @@
       <c r="AQ24" s="6"/>
       <c r="AR24" s="6"/>
     </row>
-    <row r="25" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="3"/>
       <c r="B25" s="3" t="s">
         <v>39</v>
@@ -2920,7 +2942,7 @@
       <c r="AQ25" s="6"/>
       <c r="AR25" s="6"/>
     </row>
-    <row r="26" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="3"/>
       <c r="B26" s="3" t="s">
         <v>39</v>
@@ -2994,7 +3016,7 @@
       <c r="AQ26" s="6"/>
       <c r="AR26" s="6"/>
     </row>
-    <row r="27" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="3"/>
       <c r="B27" s="3" t="s">
         <v>39</v>
@@ -3068,7 +3090,7 @@
       <c r="AQ27" s="6"/>
       <c r="AR27" s="6"/>
     </row>
-    <row r="28" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" s="3"/>
       <c r="B28" s="3" t="s">
         <v>39</v>
@@ -3142,7 +3164,7 @@
       <c r="AQ28" s="6"/>
       <c r="AR28" s="6"/>
     </row>
-    <row r="29" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" s="3"/>
       <c r="B29" s="3" t="s">
         <v>39</v>
@@ -3216,7 +3238,7 @@
       <c r="AQ29" s="6"/>
       <c r="AR29" s="6"/>
     </row>
-    <row r="30" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="3"/>
       <c r="B30" s="3" t="s">
         <v>39</v>
@@ -3290,7 +3312,7 @@
       <c r="AQ30" s="6"/>
       <c r="AR30" s="6"/>
     </row>
-    <row r="31" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A31" s="3"/>
       <c r="B31" s="3" t="s">
         <v>39</v>
@@ -3364,7 +3386,7 @@
       <c r="AQ31" s="6"/>
       <c r="AR31" s="6"/>
     </row>
-    <row r="32" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A32" s="3"/>
       <c r="B32" s="3" t="s">
         <v>39</v>
@@ -3438,7 +3460,7 @@
       <c r="AQ32" s="6"/>
       <c r="AR32" s="6"/>
     </row>
-    <row r="33" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A33" s="3"/>
       <c r="B33" s="3" t="s">
         <v>39</v>
@@ -3512,7 +3534,7 @@
       <c r="AQ33" s="6"/>
       <c r="AR33" s="6"/>
     </row>
-    <row r="34" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A34" s="3"/>
       <c r="B34" s="3" t="s">
         <v>39</v>
@@ -3586,7 +3608,7 @@
       <c r="AQ34" s="6"/>
       <c r="AR34" s="6"/>
     </row>
-    <row r="35" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A35" s="3"/>
       <c r="B35" s="3" t="s">
         <v>39</v>
@@ -3660,7 +3682,7 @@
       <c r="AQ35" s="6"/>
       <c r="AR35" s="6"/>
     </row>
-    <row r="36" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A36" s="3"/>
       <c r="B36" s="3" t="s">
         <v>39</v>
@@ -3734,7 +3756,7 @@
       <c r="AQ36" s="6"/>
       <c r="AR36" s="6"/>
     </row>
-    <row r="37" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A37" s="3"/>
       <c r="B37" s="3" t="s">
         <v>39</v>
@@ -3808,7 +3830,7 @@
       <c r="AQ37" s="6"/>
       <c r="AR37" s="6"/>
     </row>
-    <row r="38" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A38" s="3"/>
       <c r="B38" s="3" t="s">
         <v>39</v>
@@ -3882,7 +3904,7 @@
       <c r="AQ38" s="6"/>
       <c r="AR38" s="6"/>
     </row>
-    <row r="39" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A39" s="3"/>
       <c r="B39" s="3" t="s">
         <v>39</v>
@@ -3956,7 +3978,7 @@
       <c r="AQ39" s="6"/>
       <c r="AR39" s="6"/>
     </row>
-    <row r="40" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A40" s="3"/>
       <c r="B40" s="3" t="s">
         <v>39</v>
@@ -4030,7 +4052,7 @@
       <c r="AQ40" s="6"/>
       <c r="AR40" s="6"/>
     </row>
-    <row r="41" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A41" s="3"/>
       <c r="B41" s="3" t="s">
         <v>39</v>
@@ -4104,7 +4126,7 @@
       <c r="AQ41" s="6"/>
       <c r="AR41" s="6"/>
     </row>
-    <row r="42" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A42" s="3"/>
       <c r="B42" s="3" t="s">
         <v>39</v>
@@ -4178,7 +4200,7 @@
       <c r="AQ42" s="6"/>
       <c r="AR42" s="6"/>
     </row>
-    <row r="43" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A43" s="3"/>
       <c r="B43" s="3" t="s">
         <v>39</v>
@@ -4252,7 +4274,7 @@
       <c r="AQ43" s="6"/>
       <c r="AR43" s="6"/>
     </row>
-    <row r="44" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A44" s="3"/>
       <c r="B44" s="3" t="s">
         <v>39</v>
@@ -4324,7 +4346,7 @@
       <c r="AQ44" s="6"/>
       <c r="AR44" s="6"/>
     </row>
-    <row r="45" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A45" s="3"/>
       <c r="B45" s="3" t="s">
         <v>39</v>
@@ -4396,7 +4418,7 @@
       <c r="AQ45" s="6"/>
       <c r="AR45" s="6"/>
     </row>
-    <row r="46" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A46" s="3"/>
       <c r="B46" s="3" t="s">
         <v>39</v>
@@ -4472,7 +4494,7 @@
       <c r="AQ46" s="6"/>
       <c r="AR46" s="6"/>
     </row>
-    <row r="47" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A47" s="3"/>
       <c r="B47" s="3" t="s">
         <v>39</v>
@@ -4548,7 +4570,7 @@
       <c r="AQ47" s="6"/>
       <c r="AR47" s="6"/>
     </row>
-    <row r="48" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A48" s="3"/>
       <c r="B48" s="3" t="s">
         <v>39</v>
@@ -4622,7 +4644,7 @@
       <c r="AQ48" s="6"/>
       <c r="AR48" s="6"/>
     </row>
-    <row r="49" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A49" s="3"/>
       <c r="B49" s="3" t="s">
         <v>39</v>
@@ -4696,7 +4718,7 @@
       <c r="AQ49" s="6"/>
       <c r="AR49" s="6"/>
     </row>
-    <row r="50" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A50" s="3"/>
       <c r="B50" s="3" t="s">
         <v>39</v>
@@ -4777,7 +4799,7 @@
       <c r="AQ50" s="6"/>
       <c r="AR50" s="6"/>
     </row>
-    <row r="51" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A51" s="3"/>
       <c r="B51" s="3" t="s">
         <v>39</v>
@@ -4858,7 +4880,7 @@
       <c r="AQ51" s="6"/>
       <c r="AR51" s="6"/>
     </row>
-    <row r="52" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A52" s="3"/>
       <c r="B52" s="3" t="s">
         <v>39</v>
@@ -4939,7 +4961,7 @@
       <c r="AQ52" s="6"/>
       <c r="AR52" s="6"/>
     </row>
-    <row r="53" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A53" s="3"/>
       <c r="B53" s="3" t="s">
         <v>39</v>
@@ -5020,7 +5042,7 @@
       <c r="AQ53" s="6"/>
       <c r="AR53" s="6"/>
     </row>
-    <row r="54" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A54" s="3"/>
       <c r="B54" s="3" t="s">
         <v>39</v>
@@ -5094,7 +5116,7 @@
       <c r="AQ54" s="6"/>
       <c r="AR54" s="6"/>
     </row>
-    <row r="55" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A55" s="3"/>
       <c r="B55" s="3" t="s">
         <v>39</v>
@@ -5168,7 +5190,7 @@
       <c r="AQ55" s="6"/>
       <c r="AR55" s="6"/>
     </row>
-    <row r="56" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A56" s="3"/>
       <c r="B56" s="3" t="s">
         <v>39</v>
@@ -5240,7 +5262,7 @@
       <c r="AQ56" s="6"/>
       <c r="AR56" s="6"/>
     </row>
-    <row r="57" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A57" s="3"/>
       <c r="B57" s="3" t="s">
         <v>39</v>
@@ -5312,7 +5334,7 @@
       <c r="AQ57" s="6"/>
       <c r="AR57" s="6"/>
     </row>
-    <row r="58" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A58" s="3"/>
       <c r="B58" s="3" t="s">
         <v>39</v>
@@ -5384,7 +5406,7 @@
       <c r="AQ58" s="6"/>
       <c r="AR58" s="6"/>
     </row>
-    <row r="59" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A59" s="3"/>
       <c r="B59" s="3" t="s">
         <v>39</v>
@@ -5465,7 +5487,7 @@
       <c r="AQ59" s="6"/>
       <c r="AR59" s="6"/>
     </row>
-    <row r="60" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A60" s="3"/>
       <c r="B60" s="3" t="s">
         <v>39</v>
@@ -5546,7 +5568,7 @@
       <c r="AQ60" s="6"/>
       <c r="AR60" s="6"/>
     </row>
-    <row r="61" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A61" s="3"/>
       <c r="B61" s="3" t="s">
         <v>39</v>
@@ -5620,7 +5642,7 @@
       <c r="AQ61" s="6"/>
       <c r="AR61" s="6"/>
     </row>
-    <row r="62" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A62" s="3"/>
       <c r="B62" s="3" t="s">
         <v>39</v>
@@ -5694,7 +5716,7 @@
       <c r="AQ62" s="6"/>
       <c r="AR62" s="6"/>
     </row>
-    <row r="63" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A63" s="3"/>
       <c r="B63" s="3" t="s">
         <v>39</v>
@@ -5766,7 +5788,7 @@
       <c r="AQ63" s="6"/>
       <c r="AR63" s="6"/>
     </row>
-    <row r="64" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A64" s="3"/>
       <c r="B64" s="3" t="s">
         <v>39</v>
@@ -5838,7 +5860,7 @@
       <c r="AQ64" s="6"/>
       <c r="AR64" s="6"/>
     </row>
-    <row r="65" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A65" s="3"/>
       <c r="B65" s="3" t="s">
         <v>39</v>
@@ -5910,7 +5932,7 @@
       <c r="AQ65" s="6"/>
       <c r="AR65" s="6"/>
     </row>
-    <row r="66" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A66" s="3"/>
       <c r="B66" s="3" t="s">
         <v>39</v>
@@ -5982,7 +6004,7 @@
       <c r="AQ66" s="6"/>
       <c r="AR66" s="6"/>
     </row>
-    <row r="67" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A67" s="3"/>
       <c r="B67" s="3" t="s">
         <v>39</v>
@@ -6063,7 +6085,7 @@
       <c r="AQ67" s="6"/>
       <c r="AR67" s="6"/>
     </row>
-    <row r="68" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A68" s="3"/>
       <c r="B68" s="3" t="s">
         <v>39</v>
@@ -6144,7 +6166,7 @@
       <c r="AQ68" s="6"/>
       <c r="AR68" s="6"/>
     </row>
-    <row r="69" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A69" s="3"/>
       <c r="B69" s="3" t="s">
         <v>39</v>
@@ -6216,7 +6238,7 @@
       <c r="AQ69" s="6"/>
       <c r="AR69" s="6"/>
     </row>
-    <row r="70" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A70" s="3"/>
       <c r="B70" s="3" t="s">
         <v>39</v>
@@ -6288,7 +6310,7 @@
       <c r="AQ70" s="6"/>
       <c r="AR70" s="6"/>
     </row>
-    <row r="71" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A71" s="3"/>
       <c r="B71" s="3" t="s">
         <v>39</v>
@@ -6360,7 +6382,7 @@
       <c r="AQ71" s="6"/>
       <c r="AR71" s="6"/>
     </row>
-    <row r="72" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A72" s="3"/>
       <c r="B72" s="3" t="s">
         <v>39</v>
@@ -6436,7 +6458,7 @@
       <c r="AQ72" s="6"/>
       <c r="AR72" s="6"/>
     </row>
-    <row r="73" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A73" s="3"/>
       <c r="B73" s="3" t="s">
         <v>39</v>
@@ -6512,7 +6534,7 @@
       <c r="AQ73" s="6"/>
       <c r="AR73" s="6"/>
     </row>
-    <row r="74" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A74" s="3"/>
       <c r="B74" s="3" t="s">
         <v>39</v>
@@ -6584,7 +6606,7 @@
       <c r="AQ74" s="6"/>
       <c r="AR74" s="6"/>
     </row>
-    <row r="75" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A75" s="3"/>
       <c r="B75" s="3" t="s">
         <v>39</v>
@@ -6656,7 +6678,7 @@
       <c r="AQ75" s="6"/>
       <c r="AR75" s="6"/>
     </row>
-    <row r="76" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A76" s="3"/>
       <c r="B76" s="3" t="s">
         <v>39</v>
@@ -6737,7 +6759,7 @@
       <c r="AQ76" s="6"/>
       <c r="AR76" s="6"/>
     </row>
-    <row r="77" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A77" s="3"/>
       <c r="B77" s="3" t="s">
         <v>39</v>
@@ -6808,7 +6830,7 @@
       <c r="AQ77" s="6"/>
       <c r="AR77" s="6"/>
     </row>
-    <row r="78" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A78" s="3"/>
       <c r="B78" s="3" t="s">
         <v>39</v>
@@ -6879,7 +6901,7 @@
       <c r="AQ78" s="6"/>
       <c r="AR78" s="6"/>
     </row>
-    <row r="79" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A79" s="3"/>
       <c r="B79" s="3" t="s">
         <v>39</v>
@@ -6960,7 +6982,7 @@
       <c r="AQ79" s="6"/>
       <c r="AR79" s="6"/>
     </row>
-    <row r="80" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A80" s="3"/>
       <c r="B80" s="3" t="s">
         <v>39</v>
@@ -7039,7 +7061,7 @@
       <c r="AQ80" s="6"/>
       <c r="AR80" s="6"/>
     </row>
-    <row r="81" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A81" s="3"/>
       <c r="B81" s="3" t="s">
         <v>39</v>
@@ -7111,7 +7133,7 @@
       <c r="AQ81" s="6"/>
       <c r="AR81" s="6"/>
     </row>
-    <row r="82" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A82" s="3"/>
       <c r="B82" s="3" t="s">
         <v>39</v>
@@ -7183,7 +7205,7 @@
       <c r="AQ82" s="6"/>
       <c r="AR82" s="6"/>
     </row>
-    <row r="83" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A83" s="3"/>
       <c r="B83" s="3" t="s">
         <v>39</v>
@@ -7257,7 +7279,7 @@
       <c r="AQ83" s="6"/>
       <c r="AR83" s="6"/>
     </row>
-    <row r="84" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A84" s="3"/>
       <c r="B84" s="3" t="s">
         <v>39</v>
@@ -7331,7 +7353,7 @@
       <c r="AQ84" s="6"/>
       <c r="AR84" s="6"/>
     </row>
-    <row r="85" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A85" s="3"/>
       <c r="B85" s="3" t="s">
         <v>39</v>
@@ -7403,7 +7425,7 @@
       <c r="AQ85" s="6"/>
       <c r="AR85" s="6"/>
     </row>
-    <row r="86" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A86" s="3"/>
       <c r="B86" s="3" t="s">
         <v>39</v>
@@ -7475,7 +7497,7 @@
       <c r="AQ86" s="6"/>
       <c r="AR86" s="6"/>
     </row>
-    <row r="87" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A87" s="3"/>
       <c r="B87" s="3" t="s">
         <v>39</v>
@@ -7547,7 +7569,7 @@
       <c r="AQ87" s="6"/>
       <c r="AR87" s="6"/>
     </row>
-    <row r="88" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A88" s="3"/>
       <c r="B88" s="3" t="s">
         <v>39</v>
@@ -7621,7 +7643,7 @@
       <c r="AQ88" s="6"/>
       <c r="AR88" s="6"/>
     </row>
-    <row r="89" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A89" s="3"/>
       <c r="B89" s="3" t="s">
         <v>39</v>
@@ -7699,7 +7721,7 @@
       <c r="AQ89" s="6"/>
       <c r="AR89" s="6"/>
     </row>
-    <row r="90" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A90" s="3"/>
       <c r="B90" s="3" t="s">
         <v>39</v>
@@ -7777,7 +7799,7 @@
       <c r="AQ90" s="6"/>
       <c r="AR90" s="6"/>
     </row>
-    <row r="91" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A91" s="3"/>
       <c r="B91" s="3" t="s">
         <v>39</v>
@@ -7849,7 +7871,7 @@
       <c r="AQ91" s="6"/>
       <c r="AR91" s="6"/>
     </row>
-    <row r="92" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A92" s="3"/>
       <c r="B92" s="3" t="s">
         <v>39</v>
@@ -7923,7 +7945,7 @@
       <c r="AQ92" s="6"/>
       <c r="AR92" s="6"/>
     </row>
-    <row r="93" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A93" s="3"/>
       <c r="B93" s="3" t="s">
         <v>39</v>
@@ -7997,7 +8019,7 @@
       <c r="AQ93" s="6"/>
       <c r="AR93" s="6"/>
     </row>
-    <row r="94" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A94" s="3"/>
       <c r="B94" s="3" t="s">
         <v>39</v>
@@ -8073,7 +8095,7 @@
       <c r="AQ94" s="6"/>
       <c r="AR94" s="6"/>
     </row>
-    <row r="95" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A95" s="3"/>
       <c r="B95" s="3" t="s">
         <v>39</v>
@@ -8149,7 +8171,7 @@
       <c r="AQ95" s="6"/>
       <c r="AR95" s="6"/>
     </row>
-    <row r="96" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A96" s="3"/>
       <c r="B96" s="3" t="s">
         <v>39</v>
@@ -8223,7 +8245,7 @@
       <c r="AQ96" s="6"/>
       <c r="AR96" s="6"/>
     </row>
-    <row r="97" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A97" s="3"/>
       <c r="B97" s="3" t="s">
         <v>39</v>
@@ -8295,7 +8317,7 @@
       <c r="AQ97" s="6"/>
       <c r="AR97" s="6"/>
     </row>
-    <row r="98" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A98" s="3"/>
       <c r="B98" s="3" t="s">
         <v>39</v>
@@ -8367,7 +8389,7 @@
       <c r="AQ98" s="6"/>
       <c r="AR98" s="6"/>
     </row>
-    <row r="99" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A99" s="3"/>
       <c r="B99" s="3" t="s">
         <v>39</v>
@@ -8439,7 +8461,7 @@
       <c r="AQ99" s="6"/>
       <c r="AR99" s="6"/>
     </row>
-    <row r="100" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A100" s="3"/>
       <c r="B100" s="3" t="s">
         <v>39</v>
@@ -8515,7 +8537,7 @@
       <c r="AQ100" s="6"/>
       <c r="AR100" s="6"/>
     </row>
-    <row r="101" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A101" s="3"/>
       <c r="B101" s="3" t="s">
         <v>39</v>
@@ -8591,7 +8613,7 @@
       <c r="AQ101" s="6"/>
       <c r="AR101" s="6"/>
     </row>
-    <row r="102" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A102" s="3"/>
       <c r="B102" s="3" t="s">
         <v>39</v>
@@ -8665,7 +8687,7 @@
       <c r="AQ102" s="6"/>
       <c r="AR102" s="6"/>
     </row>
-    <row r="103" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A103" s="3"/>
       <c r="B103" s="3" t="s">
         <v>39</v>
@@ -8741,7 +8763,7 @@
       <c r="AQ103" s="6"/>
       <c r="AR103" s="6"/>
     </row>
-    <row r="104" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A104" s="3"/>
       <c r="B104" s="3" t="s">
         <v>39</v>
@@ -8817,7 +8839,7 @@
       <c r="AQ104" s="6"/>
       <c r="AR104" s="6"/>
     </row>
-    <row r="105" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A105" s="3"/>
       <c r="B105" s="3" t="s">
         <v>39</v>
@@ -8893,7 +8915,7 @@
       <c r="AQ105" s="6"/>
       <c r="AR105" s="6"/>
     </row>
-    <row r="106" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A106" s="3"/>
       <c r="B106" s="3" t="s">
         <v>39</v>
@@ -8969,7 +8991,7 @@
       <c r="AQ106" s="6"/>
       <c r="AR106" s="6"/>
     </row>
-    <row r="107" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A107" s="3"/>
       <c r="B107" s="3" t="s">
         <v>39</v>
@@ -9045,7 +9067,7 @@
       <c r="AQ107" s="6"/>
       <c r="AR107" s="6"/>
     </row>
-    <row r="108" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A108" s="3"/>
       <c r="B108" s="3" t="s">
         <v>39</v>
@@ -9121,7 +9143,7 @@
       <c r="AQ108" s="6"/>
       <c r="AR108" s="6"/>
     </row>
-    <row r="109" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A109" s="3"/>
       <c r="B109" s="3" t="s">
         <v>39</v>
@@ -9197,7 +9219,7 @@
       <c r="AQ109" s="6"/>
       <c r="AR109" s="6"/>
     </row>
-    <row r="110" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A110" s="3"/>
       <c r="B110" s="3" t="s">
         <v>39</v>
@@ -9273,7 +9295,7 @@
       <c r="AQ110" s="6"/>
       <c r="AR110" s="6"/>
     </row>
-    <row r="111" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A111" s="3"/>
       <c r="B111" s="3" t="s">
         <v>39</v>
@@ -9349,7 +9371,7 @@
       <c r="AQ111" s="6"/>
       <c r="AR111" s="6"/>
     </row>
-    <row r="112" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A112" s="3"/>
       <c r="B112" s="3" t="s">
         <v>39</v>
@@ -9425,7 +9447,7 @@
       <c r="AQ112" s="6"/>
       <c r="AR112" s="6"/>
     </row>
-    <row r="113" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A113" s="3"/>
       <c r="B113" s="3" t="s">
         <v>39</v>
@@ -9501,7 +9523,7 @@
       <c r="AQ113" s="6"/>
       <c r="AR113" s="6"/>
     </row>
-    <row r="114" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A114" s="3"/>
       <c r="B114" s="3" t="s">
         <v>39</v>
@@ -9577,7 +9599,7 @@
       <c r="AQ114" s="6"/>
       <c r="AR114" s="6"/>
     </row>
-    <row r="115" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A115" s="3"/>
       <c r="B115" s="3" t="s">
         <v>39</v>
@@ -9653,7 +9675,7 @@
       <c r="AQ115" s="6"/>
       <c r="AR115" s="6"/>
     </row>
-    <row r="116" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A116" s="3"/>
       <c r="B116" s="3" t="s">
         <v>39</v>
@@ -9729,7 +9751,7 @@
       <c r="AQ116" s="6"/>
       <c r="AR116" s="6"/>
     </row>
-    <row r="117" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A117" s="3"/>
       <c r="B117" s="3" t="s">
         <v>39</v>
@@ -9805,7 +9827,7 @@
       <c r="AQ117" s="6"/>
       <c r="AR117" s="6"/>
     </row>
-    <row r="118" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A118" s="3"/>
       <c r="B118" s="3" t="s">
         <v>39</v>
@@ -9881,7 +9903,7 @@
       <c r="AQ118" s="6"/>
       <c r="AR118" s="6"/>
     </row>
-    <row r="119" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A119" s="3"/>
       <c r="B119" s="3" t="s">
         <v>39</v>
@@ -9957,7 +9979,7 @@
       <c r="AQ119" s="6"/>
       <c r="AR119" s="6"/>
     </row>
-    <row r="120" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A120" s="3"/>
       <c r="B120" s="3" t="s">
         <v>39</v>
@@ -10033,7 +10055,7 @@
       <c r="AQ120" s="6"/>
       <c r="AR120" s="6"/>
     </row>
-    <row r="121" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A121" s="3"/>
       <c r="B121" s="3" t="s">
         <v>39</v>
@@ -10109,7 +10131,7 @@
       <c r="AQ121" s="6"/>
       <c r="AR121" s="6"/>
     </row>
-    <row r="122" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A122" s="3"/>
       <c r="B122" s="3" t="s">
         <v>39</v>
@@ -10185,7 +10207,7 @@
       <c r="AQ122" s="6"/>
       <c r="AR122" s="6"/>
     </row>
-    <row r="123" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A123" s="3"/>
       <c r="B123" s="3" t="s">
         <v>39</v>
@@ -10261,7 +10283,7 @@
       <c r="AQ123" s="6"/>
       <c r="AR123" s="6"/>
     </row>
-    <row r="124" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A124" s="3"/>
       <c r="B124" s="3" t="s">
         <v>39</v>
@@ -10337,7 +10359,7 @@
       <c r="AQ124" s="6"/>
       <c r="AR124" s="6"/>
     </row>
-    <row r="125" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A125" s="3"/>
       <c r="B125" s="3" t="s">
         <v>39</v>
@@ -10413,7 +10435,7 @@
       <c r="AQ125" s="6"/>
       <c r="AR125" s="6"/>
     </row>
-    <row r="126" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A126" s="3"/>
       <c r="B126" s="3" t="s">
         <v>39</v>
@@ -10489,7 +10511,7 @@
       <c r="AQ126" s="6"/>
       <c r="AR126" s="6"/>
     </row>
-    <row r="127" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A127" s="3"/>
       <c r="B127" s="3" t="s">
         <v>39</v>
@@ -10565,7 +10587,7 @@
       <c r="AQ127" s="6"/>
       <c r="AR127" s="6"/>
     </row>
-    <row r="128" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A128" s="3"/>
       <c r="B128" s="3" t="s">
         <v>39</v>
@@ -10641,7 +10663,7 @@
       <c r="AQ128" s="6"/>
       <c r="AR128" s="6"/>
     </row>
-    <row r="129" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A129" s="3"/>
       <c r="B129" s="3" t="s">
         <v>39</v>
@@ -10717,7 +10739,7 @@
       <c r="AQ129" s="6"/>
       <c r="AR129" s="6"/>
     </row>
-    <row r="130" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A130" s="3"/>
       <c r="B130" s="3" t="s">
         <v>39</v>
@@ -10793,7 +10815,7 @@
       <c r="AQ130" s="6"/>
       <c r="AR130" s="6"/>
     </row>
-    <row r="131" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A131" s="3"/>
       <c r="B131" s="3" t="s">
         <v>39</v>
@@ -10869,7 +10891,7 @@
       <c r="AQ131" s="6"/>
       <c r="AR131" s="6"/>
     </row>
-    <row r="132" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A132" s="3"/>
       <c r="B132" s="3" t="s">
         <v>39</v>
@@ -10945,7 +10967,7 @@
       <c r="AQ132" s="6"/>
       <c r="AR132" s="6"/>
     </row>
-    <row r="133" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A133" s="3"/>
       <c r="B133" s="3" t="s">
         <v>39</v>
@@ -11021,7 +11043,7 @@
       <c r="AQ133" s="6"/>
       <c r="AR133" s="6"/>
     </row>
-    <row r="134" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A134" s="3"/>
       <c r="B134" s="3" t="s">
         <v>39</v>
@@ -11097,7 +11119,7 @@
       <c r="AQ134" s="6"/>
       <c r="AR134" s="6"/>
     </row>
-    <row r="135" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A135" s="3"/>
       <c r="B135" s="3" t="s">
         <v>39</v>
@@ -11173,7 +11195,7 @@
       <c r="AQ135" s="6"/>
       <c r="AR135" s="6"/>
     </row>
-    <row r="136" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A136" s="3"/>
       <c r="B136" s="3" t="s">
         <v>39</v>
@@ -11249,7 +11271,7 @@
       <c r="AQ136" s="6"/>
       <c r="AR136" s="6"/>
     </row>
-    <row r="137" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A137" s="3"/>
       <c r="B137" s="3" t="s">
         <v>39</v>
@@ -11325,7 +11347,7 @@
       <c r="AQ137" s="6"/>
       <c r="AR137" s="6"/>
     </row>
-    <row r="138" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A138" s="3"/>
       <c r="B138" s="3" t="s">
         <v>39</v>
@@ -11401,7 +11423,7 @@
       <c r="AQ138" s="6"/>
       <c r="AR138" s="6"/>
     </row>
-    <row r="139" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A139" s="3"/>
       <c r="B139" s="3" t="s">
         <v>39</v>
@@ -11477,7 +11499,7 @@
       <c r="AQ139" s="6"/>
       <c r="AR139" s="6"/>
     </row>
-    <row r="140" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A140" s="3"/>
       <c r="B140" s="3" t="s">
         <v>39</v>
@@ -11553,7 +11575,7 @@
       <c r="AQ140" s="6"/>
       <c r="AR140" s="6"/>
     </row>
-    <row r="141" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A141" s="3"/>
       <c r="B141" s="3" t="s">
         <v>39</v>
@@ -11629,7 +11651,7 @@
       <c r="AQ141" s="6"/>
       <c r="AR141" s="6"/>
     </row>
-    <row r="142" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A142" s="3"/>
       <c r="B142" s="3" t="s">
         <v>39</v>
@@ -11705,7 +11727,7 @@
       <c r="AQ142" s="6"/>
       <c r="AR142" s="6"/>
     </row>
-    <row r="143" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A143" s="3"/>
       <c r="B143" s="3" t="s">
         <v>39</v>
@@ -11781,7 +11803,7 @@
       <c r="AQ143" s="6"/>
       <c r="AR143" s="6"/>
     </row>
-    <row r="144" spans="1:44" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:44" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A144" s="3"/>
       <c r="B144" s="3" t="s">
         <v>39</v>
@@ -11857,7 +11879,7 @@
       <c r="AQ144" s="6"/>
       <c r="AR144" s="6"/>
     </row>
-    <row r="145" spans="1:48" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:51" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A145" s="3"/>
       <c r="B145" s="3" t="s">
         <v>39</v>
@@ -11933,7 +11955,7 @@
       <c r="AQ145" s="6"/>
       <c r="AR145" s="6"/>
     </row>
-    <row r="146" spans="1:48" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:51" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A146" s="3"/>
       <c r="B146" s="3" t="s">
         <v>39</v>
@@ -12009,7 +12031,7 @@
       <c r="AQ146" s="6"/>
       <c r="AR146" s="6"/>
     </row>
-    <row r="147" spans="1:48" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:51" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A147" s="3"/>
       <c r="B147" s="3" t="s">
         <v>39</v>
@@ -12085,7 +12107,7 @@
       <c r="AQ147" s="6"/>
       <c r="AR147" s="6"/>
     </row>
-    <row r="148" spans="1:48" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:51" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A148" s="3"/>
       <c r="B148" s="3" t="s">
         <v>39</v>
@@ -12161,7 +12183,7 @@
       <c r="AQ148" s="6"/>
       <c r="AR148" s="6"/>
     </row>
-    <row r="149" spans="1:48" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:51" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A149" s="3"/>
       <c r="B149" s="3" t="s">
         <v>39</v>
@@ -12237,7 +12259,7 @@
       <c r="AQ149" s="6"/>
       <c r="AR149" s="6"/>
     </row>
-    <row r="150" spans="1:48" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:51" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A150" s="3"/>
       <c r="B150" s="3" t="s">
         <v>39</v>
@@ -12313,7 +12335,7 @@
       <c r="AQ150" s="6"/>
       <c r="AR150" s="6"/>
     </row>
-    <row r="151" spans="1:48" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:51" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A151" s="3"/>
       <c r="B151" s="3" t="s">
         <v>39</v>
@@ -12389,7 +12411,7 @@
       <c r="AQ151" s="6"/>
       <c r="AR151" s="6"/>
     </row>
-    <row r="152" spans="1:48" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:51" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A152" s="3"/>
       <c r="B152" s="3" t="s">
         <v>39</v>
@@ -12465,7 +12487,7 @@
       <c r="AQ152" s="6"/>
       <c r="AR152" s="6"/>
     </row>
-    <row r="153" spans="1:48" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:51" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A153" s="3"/>
       <c r="B153" s="3" t="s">
         <v>39</v>
@@ -12541,7 +12563,7 @@
       <c r="AQ153" s="6"/>
       <c r="AR153" s="6"/>
     </row>
-    <row r="154" spans="1:48" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:51" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A154" s="3"/>
       <c r="B154" s="3" t="s">
         <v>39</v>
@@ -12617,7 +12639,7 @@
       <c r="AQ154" s="6"/>
       <c r="AR154" s="6"/>
     </row>
-    <row r="155" spans="1:48" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:51" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A155" s="3"/>
       <c r="B155" s="3" t="s">
         <v>39</v>
@@ -12693,7 +12715,7 @@
       <c r="AQ155" s="6"/>
       <c r="AR155" s="6"/>
     </row>
-    <row r="156" spans="1:48" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:51" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A156" s="3"/>
       <c r="B156" s="3" t="s">
         <v>39</v>
@@ -12769,7 +12791,7 @@
       <c r="AQ156" s="6"/>
       <c r="AR156" s="6"/>
     </row>
-    <row r="157" spans="1:48" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:51" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A157" s="3"/>
       <c r="B157" s="3" t="s">
         <v>39</v>
@@ -12845,7 +12867,7 @@
       <c r="AQ157" s="6"/>
       <c r="AR157" s="6"/>
     </row>
-    <row r="158" spans="1:48" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:51" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A158" s="3"/>
       <c r="B158" s="3" t="s">
         <v>39</v>
@@ -12916,14 +12938,47 @@
       <c r="AJ158" s="3"/>
       <c r="AK158" s="3"/>
       <c r="AL158" s="3"/>
-      <c r="AM158" s="3"/>
-      <c r="AN158" s="3"/>
-      <c r="AO158" s="6"/>
-      <c r="AP158" s="6"/>
-      <c r="AQ158" s="6"/>
-      <c r="AR158" s="6"/>
-    </row>
-    <row r="159" spans="1:48" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM158" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="AN158" s="3">
+        <v>0.27500000000000002</v>
+      </c>
+      <c r="AO158" s="6">
+        <v>7.2039999999999997</v>
+      </c>
+      <c r="AP158" s="6">
+        <v>39</v>
+      </c>
+      <c r="AQ158" s="6">
+        <v>7.2039999999999997</v>
+      </c>
+      <c r="AR158" s="6">
+        <v>0.72489999999999999</v>
+      </c>
+      <c r="AS158" s="5">
+        <v>1.14E-2</v>
+      </c>
+      <c r="AT158" s="5">
+        <v>7.2039999999999997</v>
+      </c>
+      <c r="AU158" s="5">
+        <v>1.6181000000000001</v>
+      </c>
+      <c r="AV158" s="5">
+        <v>7.2039999999999997</v>
+      </c>
+      <c r="AW158" s="5">
+        <v>23.12</v>
+      </c>
+      <c r="AX158" s="5">
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="AY158" s="5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="159" spans="1:51" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A159" s="3"/>
       <c r="B159" s="3" t="s">
         <v>39</v>
@@ -12995,7 +13050,7 @@
       <c r="AK159" s="3"/>
       <c r="AL159" s="3"/>
       <c r="AM159" s="3" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="AN159" s="3">
         <v>1.14E-2</v>
@@ -13025,7 +13080,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="160" spans="1:48" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:51" s="5" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A160" s="3"/>
       <c r="B160" s="3" t="s">
         <v>39</v>
@@ -13095,7 +13150,7 @@
       <c r="AK160" s="3"/>
       <c r="AL160" s="3"/>
       <c r="AM160" s="3" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="AN160" s="3">
         <v>2.7799999999999998E-2</v>
